--- a/files/04-better-metadata.xlsx
+++ b/files/04-better-metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24422"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\ed-dash\fair-bio-practice\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/s2531396/Documents/GitHub/fair-in-circadian-practice/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54AE3CE3-446C-40B7-8D1C-626116BFA427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43E8E79-8935-7C46-A87A-36C785B9E6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="1545" windowWidth="23250" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -118,10 +118,6 @@
 (GM agar)</t>
   </si>
   <si>
-    <t xml:space="preserve">Biomas
-</t>
-  </si>
-  <si>
     <t>Starch</t>
   </si>
   <si>
@@ -425,6 +421,10 @@
   <si>
     <t>10 mg sucrose per GM-agar</t>
   </si>
+  <si>
+    <t xml:space="preserve">Biomass
+</t>
+  </si>
 </sst>
 </file>
 
@@ -434,7 +434,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -594,32 +594,19 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -628,8 +615,8 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,9 +635,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -688,7 +675,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -794,7 +781,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -936,7 +923,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -945,97 +932,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="29" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29" t="s">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="35.450000000000003" customHeight="1">
+    <row r="6" spans="1:14" ht="35.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1052,668 +1014,659 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="D7" s="18" t="s">
         <v>26</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>27</v>
       </c>
       <c r="E7" s="26">
         <v>0</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="30">
         <v>0.1206</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="33">
         <v>6</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="33">
         <v>1.2</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="30">
         <v>1.8E-3</v>
       </c>
       <c r="L7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="28"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>27</v>
       </c>
       <c r="E8" s="26">
         <v>0</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="30">
         <v>0.1275</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="33">
         <v>6.5</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="33">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="30">
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" t="s">
         <v>31</v>
       </c>
-      <c r="N8" t="s">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>27</v>
+      <c r="D9" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E9" s="26">
         <v>0</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="30">
         <v>0.28720000000000001</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="33">
         <v>5</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="33">
         <v>1</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="30">
         <v>1.4E-3</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="28"/>
+        <v>25</v>
+      </c>
       <c r="N9" cm="1">
         <f t="array" ref="N9">AVERAGE(_xlfn._xlws.FILTER(F7:F26,C7:C26=L9))</f>
         <v>0.22544999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="40" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="C10" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>27</v>
+      <c r="D10" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="26">
         <v>0</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="30">
         <v>0.15240000000000001</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="33">
         <v>3</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="33">
         <v>0.6</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="30">
         <v>2E-3</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="28"/>
+        <v>34</v>
+      </c>
       <c r="N10" cm="1">
         <f t="array" ref="N10">AVERAGE(_xlfn._xlws.FILTER(F7:F26,C7:C26=L10))</f>
         <v>0.28439999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="C11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>27</v>
+      <c r="D11" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E11" s="26">
         <v>0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="30">
         <v>0.20349999999999999</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I11" s="30">
+        <v>1.6999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="42">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I11" s="41">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="M11" s="28"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="21" t="s">
+      <c r="B12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>43</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>44</v>
       </c>
       <c r="E12" s="24">
         <v>1</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="31">
         <v>0.2104</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="34">
         <v>6.2</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="34">
         <v>1.3</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="31">
         <v>2.1000000000000003E-3</v>
       </c>
-      <c r="M12" s="28"/>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>44</v>
+        <v>25</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="E13" s="24">
         <v>1</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="31">
         <v>0.24349999999999999</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="34">
         <v>7</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="34">
         <v>1.2</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="31">
         <v>1.9E-3</v>
       </c>
-      <c r="M13" s="28"/>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>44</v>
+      <c r="D14" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="E14" s="24">
         <v>1</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="31">
         <v>0.32129999999999997</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="34">
         <v>5.8</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I14" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="M14" s="28"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="I14" s="38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>44</v>
+      <c r="D15" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="E15" s="24">
         <v>1</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="31">
         <v>0.2135</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="34">
         <v>4.9000000000000004</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="34">
         <v>0.8</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="31">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="M15" s="28"/>
-    </row>
-    <row r="16" spans="1:14">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>44</v>
+      <c r="D16" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="E16" s="24">
         <v>1</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="31">
         <v>0.29199999999999998</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="34">
         <v>5.9</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="34">
         <v>0.9</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="31">
         <v>2.1000000000000003E-3</v>
       </c>
-      <c r="M16" s="28"/>
-    </row>
-    <row r="17" spans="1:10">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="D17" s="18" t="s">
         <v>26</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>27</v>
       </c>
       <c r="E17" s="27">
         <v>1</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="30">
         <v>0.13</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="33">
         <v>6</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="33">
         <v>1.2</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="30">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>26</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>27</v>
       </c>
       <c r="E18" s="27">
         <v>1</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="30">
         <v>0.14149999999999999</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="33">
         <v>6.5</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="33">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="30">
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>27</v>
+      <c r="D19" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E19" s="27">
         <v>1</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="30">
         <v>0.28810000000000002</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="33">
         <v>5</v>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="33">
         <v>1</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="30">
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>27</v>
+      <c r="D20" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E20" s="27">
         <v>1</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="30">
         <v>0.152</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="33">
         <v>3</v>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="33">
         <v>0.6</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="30">
         <v>2E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>27</v>
+      <c r="D21" s="18" t="s">
+        <v>26</v>
       </c>
       <c r="E21" s="27">
         <v>1</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="30">
         <v>0.20399999999999999</v>
       </c>
-      <c r="G21" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="37">
+      <c r="G21" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="33">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="30">
         <v>1.6999999999999999E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0</v>
+      </c>
+      <c r="F22" s="32">
+        <v>0.1351</v>
+      </c>
+      <c r="G22" s="35">
+        <v>6</v>
+      </c>
+      <c r="H22" s="35">
+        <v>1.2</v>
+      </c>
+      <c r="I22" s="32">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="29">
+        <v>0</v>
+      </c>
+      <c r="F23" s="32">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="31">
+      <c r="D24" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="29">
         <v>0</v>
       </c>
-      <c r="F22" s="36">
-        <v>0.1351</v>
-      </c>
-      <c r="G22" s="39">
-        <v>6</v>
-      </c>
-      <c r="H22" s="39">
-        <v>1.2</v>
-      </c>
-      <c r="I22" s="36">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="31">
+      <c r="F24" s="32">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="G24" s="35">
+        <v>7</v>
+      </c>
+      <c r="H24" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I24" s="32">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="29">
         <v>0</v>
       </c>
-      <c r="F23" s="36">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="31">
+      <c r="F25" s="32">
+        <v>0.14249999999999999</v>
+      </c>
+      <c r="G25" s="35">
+        <v>3.1</v>
+      </c>
+      <c r="H25" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="I25" s="32">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="29">
         <v>0</v>
       </c>
-      <c r="F24" s="36">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="G24" s="39">
-        <v>7</v>
-      </c>
-      <c r="H24" s="39">
+      <c r="F26" s="32">
+        <v>0.2041</v>
+      </c>
+      <c r="G26" s="35">
+        <v>5</v>
+      </c>
+      <c r="H26" s="35">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I24" s="36">
-        <v>2.0999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="31">
-        <v>0</v>
-      </c>
-      <c r="F25" s="36">
-        <v>0.14249999999999999</v>
-      </c>
-      <c r="G25" s="39">
-        <v>3.1</v>
-      </c>
-      <c r="H25" s="39">
-        <v>0.6</v>
-      </c>
-      <c r="I25" s="36">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="16" t="s">
+      <c r="I26" s="32">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="31">
-        <v>0</v>
-      </c>
-      <c r="F26" s="36">
-        <v>0.2041</v>
-      </c>
-      <c r="G26" s="39">
-        <v>5</v>
-      </c>
-      <c r="H26" s="39">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I26" s="36">
-        <v>1.1000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="19" t="s">
+      <c r="B27" s="20" t="s">
         <v>59</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>60</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
     </row>
   </sheetData>
@@ -1725,19 +1678,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1751,16 +1704,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -1769,47 +1722,47 @@
       </c>
       <c r="C3" s="8"/>
       <c r="F3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="C4" s="7"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
@@ -1818,68 +1771,68 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="35.450000000000003" customHeight="1">
+    </row>
+    <row r="8" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F9" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>87</v>
       </c>
       <c r="G9">
         <v>0.1206</v>
@@ -1894,24 +1847,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>87</v>
       </c>
       <c r="G10">
         <v>0.1275</v>
@@ -1926,24 +1879,24 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11">
         <v>0.28720000000000001</v>
@@ -1958,24 +1911,24 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G12">
         <v>0.15240000000000001</v>
@@ -1990,30 +1943,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>41</v>
-      </c>
       <c r="D13" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13">
         <v>0.20349999999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I13">
         <v>1.1000000000000001</v>
@@ -2022,24 +1975,24 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14">
         <v>0.2104</v>
@@ -2054,24 +2007,24 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15">
         <v>0.24349999999999999</v>
@@ -2086,24 +2039,24 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="D16" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>0.32129999999999997</v>
@@ -2115,27 +2068,27 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="J16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="D17" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17">
         <v>0.2135</v>
@@ -2150,24 +2103,24 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="G18">
         <v>0.29199999999999998</v>
@@ -2182,39 +2135,39 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="9"/>
       <c r="E20" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="15" t="s">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="14" t="s">
+      <c r="B22" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C22" s="9"/>
     </row>
